--- a/practice.xlsx
+++ b/practice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e43f172441098b51/Desktop/Excel_first/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEEFE1FA-D7EE-4B04-B109-7BAF0E35D606}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{E5A8AFDF-4C2B-4EF7-9F1C-64D71BC673BF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Shashi</t>
   </si>
@@ -171,6 +171,24 @@
   </si>
   <si>
     <t>sumifs</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Averageif</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>counta</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>countblank</t>
   </si>
 </sst>
 </file>
@@ -247,8 +265,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}" name="Table1" displayName="Table1" ref="C4:G13" totalsRowShown="0">
-  <autoFilter ref="C4:G13" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}" name="Table1" displayName="Table1" ref="C4:G14" totalsRowShown="0">
+  <autoFilter ref="C4:G14" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A6B0653E-CA82-4432-A5F6-E15402ED067B}" name="Roll No"/>
     <tableColumn id="2" xr3:uid="{8AA466D1-E11F-4916-9D39-98595DA9EC44}" name="Name"/>
@@ -722,7 +740,7 @@
       </c>
       <c r="D5" s="4">
         <f ca="1">NOW()</f>
-        <v>46303.851437152778</v>
+        <v>46303.86516828704</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
@@ -793,8 +811,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC80CE97-5069-4B2C-852A-A81206AF3003}">
-  <dimension ref="C4:L13"/>
+  <dimension ref="C4:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="4" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
@@ -857,6 +878,10 @@
       <c r="K6" t="s">
         <v>44</v>
       </c>
+      <c r="L6">
+        <f>SUMIFS(Table1[Marks],Table1[City],"Mumbai",Table1[Marks],"&gt;70")</f>
+        <v>89</v>
+      </c>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C7">
@@ -871,6 +896,13 @@
       <c r="F7" t="s">
         <v>33</v>
       </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7">
+        <f>AVERAGE(Table1[Marks])</f>
+        <v>78.666666666666671</v>
+      </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C8">
@@ -885,6 +917,13 @@
       <c r="F8" t="s">
         <v>35</v>
       </c>
+      <c r="K8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8">
+        <f>AVERAGEIF(Table1[Marks],"&gt;70")</f>
+        <v>85.142857142857139</v>
+      </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C9">
@@ -899,6 +938,13 @@
       <c r="F9" t="s">
         <v>36</v>
       </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9">
+        <f>COUNT(Table1[Roll No])</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C10">
@@ -913,6 +959,13 @@
       <c r="F10" t="s">
         <v>35</v>
       </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10">
+        <f>COUNTA(Table1[Roll No])</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C11">
@@ -927,6 +980,13 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
+      <c r="K11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11">
+        <f>COUNTBLANK(C5:C15)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C12">
@@ -954,6 +1014,11 @@
       </c>
       <c r="F13" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/practice.xlsx
+++ b/practice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e43f172441098b51/Desktop/Excel_first/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEEFE1FA-D7EE-4B04-B109-7BAF0E35D606}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{023FBBC8-225C-418F-AC31-B7E50808137A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{E5A8AFDF-4C2B-4EF7-9F1C-64D71BC673BF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Shashi</t>
   </si>
@@ -185,10 +185,19 @@
     <t>counta</t>
   </si>
   <si>
-    <t>hello</t>
-  </si>
-  <si>
     <t>countblank</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t>0r</t>
+  </si>
+  <si>
+    <t>if error</t>
   </si>
 </sst>
 </file>
@@ -239,19 +248,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -264,15 +290,30 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}" name="Table1" displayName="Table1" ref="C4:G14" totalsRowShown="0">
-  <autoFilter ref="C4:G14" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}" name="Table1" displayName="Table1" ref="C4:J13" totalsRowShown="0">
+  <autoFilter ref="C4:J13" xr:uid="{56911E11-08A8-4610-9FE4-6E5B4F891A9E}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A6B0653E-CA82-4432-A5F6-E15402ED067B}" name="Roll No"/>
     <tableColumn id="2" xr3:uid="{8AA466D1-E11F-4916-9D39-98595DA9EC44}" name="Name"/>
     <tableColumn id="3" xr3:uid="{DDCF7F64-66EB-44A0-9F8F-114B7E458AF7}" name="Marks"/>
     <tableColumn id="4" xr3:uid="{37185CD3-B0CF-4A69-985F-3B3920FCA87E}" name="City"/>
-    <tableColumn id="5" xr3:uid="{37AE3DF9-4CBA-4A3F-A87D-31BC5F9E22E6}" name="Grade"/>
+    <tableColumn id="5" xr3:uid="{37AE3DF9-4CBA-4A3F-A87D-31BC5F9E22E6}" name="Result" dataDxfId="3">
+      <calculatedColumnFormula>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{EA2F3D91-D920-463C-B54E-953C6D49CBF3}" name="Grade" dataDxfId="2">
+      <calculatedColumnFormula>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{62B22A3C-95D6-4E3B-8BA3-2B9B0D1A11C2}" name="And" dataDxfId="1">
+      <calculatedColumnFormula>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{BE70939C-AF73-4C6C-AF2C-1BF9B0DFECF3}" name="0r" dataDxfId="0">
+      <calculatedColumnFormula>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -587,111 +628,111 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="I2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="L2" s="4"/>
+      <c r="N2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="Q2" s="1" t="s">
+      <c r="O2" s="4"/>
+      <c r="Q2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="1"/>
+      <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
         <f>LEN(B3)</f>
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="1" t="str">
         <f>TRIM(E3)</f>
         <v>shashi</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="str">
+      <c r="L3" s="1" t="str">
         <f>LEFT(K3,3)</f>
         <v>sha</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="2" t="str">
+      <c r="O3" s="1" t="str">
         <f>RIGHT(N3,3)</f>
         <v>shi</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="2" t="str">
+      <c r="R3" s="1" t="str">
         <f>MID(Q3,2,3)</f>
         <v>has</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <f>LEN(E3)</f>
         <v>9</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <f>LEN(F3)</f>
         <v>6</v>
       </c>
-      <c r="H4" s="1" t="str">
+      <c r="H4" s="4" t="str">
         <f>_xlfn.CONCAT(H3,I3)</f>
         <v>raj patil</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="C6" s="4"/>
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="str">
+      <c r="C7" s="1" t="str">
         <f>UPPER(B7)</f>
         <v>SHASHI</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="str">
+      <c r="F7" s="1" t="str">
         <f>LOWER(E7)</f>
         <v>shashi</v>
       </c>
@@ -729,25 +770,25 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <f ca="1">NOW()</f>
-        <v>46303.86516828704</v>
+        <v>46304.822819328707</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>DATE(2029,12,23)</f>
         <v>47475</v>
       </c>
@@ -783,7 +824,7 @@
       </c>
       <c r="D9">
         <f ca="1">WEEKDAY(D4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">
@@ -811,13 +852,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC80CE97-5069-4B2C-852A-A81206AF3003}">
-  <dimension ref="C4:L14"/>
+  <dimension ref="C4:P17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>37</v>
       </c>
@@ -831,17 +872,26 @@
         <v>40</v>
       </c>
       <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
         <v>41</v>
       </c>
-      <c r="K4" t="s">
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" t="s">
         <v>42</v>
       </c>
-      <c r="L4">
+      <c r="P4">
         <f>SUM(Table1[Marks])</f>
-        <v>708</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>11</v>
       </c>
@@ -854,15 +904,31 @@
       <c r="F5" t="s">
         <v>33</v>
       </c>
-      <c r="K5" t="s">
+      <c r="G5" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H5" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>D</v>
+      </c>
+      <c r="I5" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
         <v>43</v>
       </c>
-      <c r="L5">
+      <c r="P5">
         <f>SUMIF(Table1[City],"Mumbai",Table1[Marks])</f>
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>12</v>
       </c>
@@ -875,15 +941,31 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="K6" t="s">
+      <c r="G6" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>B</v>
+      </c>
+      <c r="I6" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
         <v>44</v>
       </c>
-      <c r="L6">
+      <c r="P6">
         <f>SUMIFS(Table1[Marks],Table1[City],"Mumbai",Table1[Marks],"&gt;70")</f>
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>13</v>
       </c>
@@ -896,15 +978,31 @@
       <c r="F7" t="s">
         <v>33</v>
       </c>
-      <c r="K7" t="s">
+      <c r="G7" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>B</v>
+      </c>
+      <c r="I7" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
         <v>45</v>
       </c>
-      <c r="L7">
+      <c r="P7">
         <f>AVERAGE(Table1[Marks])</f>
-        <v>78.666666666666671</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+        <v>72.444444444444443</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>14</v>
       </c>
@@ -917,15 +1015,31 @@
       <c r="F8" t="s">
         <v>35</v>
       </c>
-      <c r="K8" t="s">
+      <c r="G8" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H8" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>C</v>
+      </c>
+      <c r="I8" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
         <v>46</v>
       </c>
-      <c r="L8">
+      <c r="P8">
         <f>AVERAGEIF(Table1[Marks],"&gt;70")</f>
-        <v>85.142857142857139</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
+        <v>84.333333333333329</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>15</v>
       </c>
@@ -933,20 +1047,36 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
       </c>
-      <c r="K9" t="s">
+      <c r="G9" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="H9" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>F</v>
+      </c>
+      <c r="I9" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
         <v>47</v>
       </c>
-      <c r="L9">
+      <c r="P9">
         <f>COUNT(Table1[Roll No])</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>16</v>
       </c>
@@ -959,15 +1089,31 @@
       <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="K10" t="s">
+      <c r="G10" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H10" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>A</v>
+      </c>
+      <c r="I10" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
         <v>48</v>
       </c>
-      <c r="L10">
+      <c r="P10">
         <f>COUNTA(Table1[Roll No])</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>17</v>
       </c>
@@ -980,15 +1126,31 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="K11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11">
-        <f>COUNTBLANK(C5:C15)</f>
+      <c r="G11" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>C</v>
+      </c>
+      <c r="I11" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P11">
+        <f>COUNTBLANK(C5:C14)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>18</v>
       </c>
@@ -1001,8 +1163,24 @@
       <c r="F12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="G12" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>D</v>
+      </c>
+      <c r="I12" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>19</v>
       </c>
@@ -1015,13 +1193,43 @@
       <c r="F13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>49</v>
+      <c r="G13" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="H13" t="str">
+        <f>IF(Table1[[#This Row],[Marks]]&gt;90,"A",IF(Table1[[#This Row],[Marks]]&gt;80,"B",IF(Table1[[#This Row],[Marks]]&gt;60,"C",IF(Table1[[#This Row],[Marks]]&gt;50,"D","F"))))</f>
+        <v>C</v>
+      </c>
+      <c r="I13" t="b">
+        <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="b">
+        <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17" t="e">
+        <f>6/0</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D17">
+        <f>IFERROR(4/0,0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C16:D16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/practice.xlsx
+++ b/practice.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e43f172441098b51/Desktop/Excel_first/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{023FBBC8-225C-418F-AC31-B7E50808137A}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC89F8C-A68D-4E9F-BE24-43349833170F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{E5A8AFDF-4C2B-4EF7-9F1C-64D71BC673BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{E5A8AFDF-4C2B-4EF7-9F1C-64D71BC673BF}"/>
   </bookViews>
   <sheets>
     <sheet name="TEXT-FUNCTION" sheetId="1" r:id="rId1"/>
     <sheet name="DATE FUNCTION" sheetId="2" r:id="rId2"/>
     <sheet name="CONDITIONAL FUNCTION" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="index-match fucntion" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
   <si>
     <t>Shashi</t>
   </si>
@@ -198,13 +200,130 @@
   </si>
   <si>
     <t>if error</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>Product A</t>
+  </si>
+  <si>
+    <t>Product B</t>
+  </si>
+  <si>
+    <t>Product C</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Clothing</t>
+  </si>
+  <si>
+    <t>Employe ID</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Sales ($)</t>
+  </si>
+  <si>
+    <t>Insentive</t>
+  </si>
+  <si>
+    <t>Approx. match</t>
+  </si>
+  <si>
+    <t>Vlookup-Exact Match</t>
+  </si>
+  <si>
+    <t>INDEX</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>INDEX &amp; MATCH function</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>Dynamic</t>
+  </si>
+  <si>
+    <t>vlookup</t>
+  </si>
+  <si>
+    <t>Hlookup</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,16 +331,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -244,20 +401,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -628,30 +861,30 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="F2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="I2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="N2" s="4" t="s">
+      <c r="L2" s="5"/>
+      <c r="N2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="Q2" s="4" t="s">
+      <c r="O2" s="5"/>
+      <c r="Q2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="4"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -705,21 +938,21 @@
         <f>LEN(F3)</f>
         <v>6</v>
       </c>
-      <c r="H4" s="4" t="str">
+      <c r="H4" s="5" t="str">
         <f>_xlfn.CONCAT(H3,I3)</f>
         <v>raj patil</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -772,7 +1005,7 @@
       </c>
       <c r="D4" s="2">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
@@ -781,7 +1014,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1">NOW()</f>
-        <v>46304.822819328707</v>
+        <v>46307.865766435185</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
@@ -824,7 +1057,7 @@
       </c>
       <c r="D9">
         <f ca="1">WEEKDAY(D4)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">
@@ -833,7 +1066,7 @@
       </c>
       <c r="D10">
         <f ca="1">WEEKNUM(D4)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.3">
@@ -916,7 +1149,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="b">
+      <c r="J5" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
@@ -953,7 +1186,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="b">
+      <c r="J6" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
@@ -990,7 +1223,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
-      <c r="J7" s="5" t="b">
+      <c r="J7" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
@@ -1027,7 +1260,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="b">
+      <c r="J8" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
@@ -1064,7 +1297,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="b">
+      <c r="J9" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
@@ -1101,7 +1334,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="5" t="b">
+      <c r="J10" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
@@ -1138,7 +1371,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="b">
+      <c r="J11" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
@@ -1175,7 +1408,7 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="5" t="b">
+      <c r="J12" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>1</v>
       </c>
@@ -1205,16 +1438,16 @@
         <f>AND(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="5" t="b">
+      <c r="J13" t="b">
         <f>OR(Table1[[#This Row],[Marks]]&gt;80,Table1[[#This Row],[City]]="Mumbai")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" t="e">
@@ -1235,4 +1468,654 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35F0E1D-9B50-4A52-8D3E-EED188315FC0}">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="18" max="18" width="13.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="1">
+        <v>500</v>
+      </c>
+      <c r="I2" s="1">
+        <v>88</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="15"/>
+      <c r="N2" s="16"/>
+      <c r="Q2" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="17"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="1">
+        <v>300</v>
+      </c>
+      <c r="I3" s="1">
+        <v>75</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="18"/>
+      <c r="N3" s="12"/>
+      <c r="Q3" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="1">
+        <f>INDEX(A1:I8,4,6)</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="1">
+        <v>650</v>
+      </c>
+      <c r="I4" s="1">
+        <v>95</v>
+      </c>
+      <c r="L4" s="11">
+        <f>VLOOKUP(L3,B1:I8,M10,0)</f>
+        <v>2024</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="12"/>
+      <c r="Q4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="1">
+        <f>MATCH(L3,B1:B8,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="1">
+        <v>400</v>
+      </c>
+      <c r="I5" s="1">
+        <v>60</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="R5" s="1">
+        <f>MATCH(L3,A3:I3,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="1">
+        <v>550</v>
+      </c>
+      <c r="I6" s="1">
+        <v>45</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="1">
+        <v>700</v>
+      </c>
+      <c r="I7" s="1">
+        <v>82</v>
+      </c>
+      <c r="L7" s="1">
+        <f>VLOOKUP(L3,B1:I8,8,0)</f>
+        <v>75</v>
+      </c>
+      <c r="M7" s="1">
+        <f>VLOOKUP(L3,B1:I8,7,0)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="1">
+        <v>200</v>
+      </c>
+      <c r="I8" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M10">
+        <f>MATCH(N9,B1:I1,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B14" s="6">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="M14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" s="1">
+        <f>VLOOKUP(L3,B1:I8,N15,0)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B15" s="6">
+        <v>20000</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="11">
+        <f>VLOOKUP(19000,B12:C17,2,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="M15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" s="1">
+        <f>MATCH(N13,B1:I1,0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="6">
+        <v>30000</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C17" s="6">
+        <v>5000</v>
+      </c>
+      <c r="L17" s="13"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1005</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1006</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22">
+        <f>HLOOKUP("Alice",A21:H28,7,0)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="1">
+        <v>500</v>
+      </c>
+      <c r="C27" s="1">
+        <v>300</v>
+      </c>
+      <c r="D27" s="1">
+        <v>650</v>
+      </c>
+      <c r="E27" s="1">
+        <v>400</v>
+      </c>
+      <c r="F27" s="1">
+        <v>550</v>
+      </c>
+      <c r="G27" s="1">
+        <v>700</v>
+      </c>
+      <c r="H27" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1">
+        <v>88</v>
+      </c>
+      <c r="C28" s="1">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1">
+        <v>95</v>
+      </c>
+      <c r="E28" s="1">
+        <v>60</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45</v>
+      </c>
+      <c r="G28" s="1">
+        <v>82</v>
+      </c>
+      <c r="H28" s="1">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="L2:N2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A5FAD2-782B-44A3-A05D-20E5BA6C75C0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/practice.xlsx
+++ b/practice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e43f172441098b51/Desktop/Excel_first/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC89F8C-A68D-4E9F-BE24-43349833170F}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{D3762795-6DE7-487B-9BAD-EEFD82822D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD765EE-A8C2-428D-9719-01557A643A82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{E5A8AFDF-4C2B-4EF7-9F1C-64D71BC673BF}"/>
   </bookViews>
@@ -37,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
   <si>
     <t>Shashi</t>
   </si>
@@ -307,9 +329,6 @@
     <t>INDEX &amp; MATCH function</t>
   </si>
   <si>
-    <t>score</t>
-  </si>
-  <si>
     <t>Dynamic</t>
   </si>
   <si>
@@ -317,6 +336,15 @@
   </si>
   <si>
     <t>Hlookup</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>XLOOPUP</t>
+  </si>
+  <si>
+    <t>multidetails</t>
   </si>
 </sst>
 </file>
@@ -442,17 +470,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -460,6 +482,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -472,7 +501,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -482,15 +513,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -861,30 +887,30 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="18"/>
+      <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="F2" s="18"/>
+      <c r="H2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="K2" s="5" t="s">
+      <c r="I2" s="18"/>
+      <c r="K2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="N2" s="5" t="s">
+      <c r="L2" s="18"/>
+      <c r="N2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="Q2" s="5" t="s">
+      <c r="O2" s="18"/>
+      <c r="Q2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="5"/>
+      <c r="R2" s="18"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -938,21 +964,21 @@
         <f>LEN(F3)</f>
         <v>6</v>
       </c>
-      <c r="H4" s="5" t="str">
+      <c r="H4" s="18" t="str">
         <f>_xlfn.CONCAT(H3,I3)</f>
         <v>raj patil</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="18"/>
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1005,7 +1031,7 @@
       </c>
       <c r="D4" s="2">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
@@ -1014,7 +1040,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1">NOW()</f>
-        <v>46307.865766435185</v>
+        <v>46309.805997222225</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
@@ -1057,7 +1083,7 @@
       </c>
       <c r="D9">
         <f ca="1">WEEKDAY(D4)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">
@@ -1444,10 +1470,10 @@
       </c>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="19"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" t="e">
@@ -1472,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35F0E1D-9B50-4A52-8D3E-EED188315FC0}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -1481,36 +1507,36 @@
     <col min="18" max="18" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -1538,18 +1564,17 @@
       <c r="I2" s="1">
         <v>88</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="16"/>
-      <c r="Q2" s="21" t="s">
+      <c r="M2" s="16"/>
+      <c r="N2" s="17"/>
+      <c r="Q2" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="21"/>
-      <c r="S2" s="17"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R2" s="9"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1002</v>
       </c>
@@ -1577,12 +1602,12 @@
       <c r="I3" s="1">
         <v>75</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="12"/>
-      <c r="Q3" s="19" t="s">
+      <c r="L3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M3" s="14"/>
+      <c r="N3" s="13"/>
+      <c r="Q3" s="7" t="s">
         <v>85</v>
       </c>
       <c r="R3" s="1">
@@ -1590,7 +1615,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1003</v>
       </c>
@@ -1618,21 +1643,21 @@
       <c r="I4" s="1">
         <v>95</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="12" t="str">
         <f>VLOOKUP(L3,B1:I8,M10,0)</f>
-        <v>2024</v>
-      </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="12"/>
-      <c r="Q4" s="19" t="s">
+        <v>Product A</v>
+      </c>
+      <c r="M4" s="14"/>
+      <c r="N4" s="13"/>
+      <c r="Q4" s="7" t="s">
         <v>87</v>
       </c>
       <c r="R4" s="1">
         <f>MATCH(L3,B1:B8,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1004</v>
       </c>
@@ -1660,15 +1685,15 @@
       <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="1" t="e">
         <f>MATCH(L3,A3:I3,0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1005</v>
       </c>
@@ -1696,14 +1721,14 @@
       <c r="I6" s="1">
         <v>45</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1006</v>
       </c>
@@ -1733,14 +1758,14 @@
       </c>
       <c r="L7" s="1">
         <f>VLOOKUP(L3,B1:I8,8,0)</f>
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="M7" s="1">
         <f>VLOOKUP(L3,B1:I8,7,0)</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1007</v>
       </c>
@@ -1769,95 +1794,131 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M10">
         <f>MATCH(N9,B1:I1,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F11" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6">
+      <c r="F12" s="1">
+        <f>_xlfn.XLOOKUP(L3,B1:B8,A1:A8,"not found",0)</f>
+        <v>1003</v>
+      </c>
+      <c r="G12" t="str" cm="1">
+        <f t="array" ref="G12:N12">_xlfn.XLOOKUP(L3,B1:B8,B1:I8,"Not found",0)</f>
+        <v>Carol</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="I12" t="str">
+        <v>North</v>
+      </c>
+      <c r="J12" t="str">
+        <v>January</v>
+      </c>
+      <c r="K12">
+        <v>2024</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Product A</v>
+      </c>
+      <c r="M12">
+        <v>650</v>
+      </c>
+      <c r="N12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
         <v>0</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="P13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="P14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N13" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="6">
-        <v>10000</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="M14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" s="1">
-        <f>VLOOKUP(L3,B1:I8,N15,0)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="6">
+      <c r="Q14" s="1" t="str">
+        <f>VLOOKUP(L3,B1:I8,Q15,0)</f>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="4">
         <v>20000</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>2000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <f>VLOOKUP(19000,B12:C17,2,1)</f>
         <v>1000</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="M15" s="1" t="s">
+      <c r="F15" s="13"/>
+      <c r="P15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N15" s="1">
-        <f>MATCH(N13,B1:I1,0)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="6">
+      <c r="Q15" s="1">
+        <f>MATCH(Q13,B1:I1,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="4">
         <v>30000</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>4000</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="6">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="4">
         <v>40000</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="4">
         <v>5000</v>
       </c>
-      <c r="L17" s="13"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B20" s="1">
@@ -1882,8 +1943,8 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1908,11 +1969,11 @@
         <v>80</v>
       </c>
       <c r="J21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1941,8 +2002,8 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1967,8 +2028,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1993,8 +2054,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B25" s="1">
@@ -2019,8 +2080,8 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2045,8 +2106,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B27" s="1">
@@ -2071,8 +2132,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B28" s="1">
